--- a/file_upload_forms/030_document_management_system_form--file_upload_forms.xlsx
+++ b/file_upload_forms/030_document_management_system_form--file_upload_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'document'}</t>
+          <t>document</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Document'}</t>
+          <t>Document</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'image'}</t>
+          <t>image</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Image'}</t>
+          <t>Image</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'audio'}</t>
+          <t>audio</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Audio'}</t>
+          <t>Audio</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Rejected'}</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'finance'}</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Finance'}</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
